--- a/artfynd/A 36487-2025 artfynd.xlsx
+++ b/artfynd/A 36487-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127225076</v>
       </c>
       <c r="B2" t="n">
-        <v>91541</v>
+        <v>91615</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127225066</v>
       </c>
       <c r="B3" t="n">
-        <v>91245</v>
+        <v>91319</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127225129</v>
       </c>
       <c r="B4" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127225078</v>
       </c>
       <c r="B5" t="n">
-        <v>97239</v>
+        <v>97314</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127225143</v>
+        <v>127225103</v>
       </c>
       <c r="B6" t="n">
-        <v>78980</v>
+        <v>98436</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>801472</v>
+        <v>801366</v>
       </c>
       <c r="R6" t="n">
-        <v>7404024</v>
+        <v>7404002</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127225103</v>
+        <v>127225143</v>
       </c>
       <c r="B7" t="n">
-        <v>98361</v>
+        <v>79011</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>801366</v>
+        <v>801472</v>
       </c>
       <c r="R7" t="n">
-        <v>7404002</v>
+        <v>7404024</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1260,7 +1260,7 @@
         <v>127225131</v>
       </c>
       <c r="B8" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>127225101</v>
       </c>
       <c r="B9" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>127225064</v>
       </c>
       <c r="B10" t="n">
-        <v>75075</v>
+        <v>75135</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>127225089</v>
       </c>
       <c r="B11" t="n">
-        <v>78739</v>
+        <v>78770</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>127225099</v>
       </c>
       <c r="B12" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127225070</v>
+        <v>127225133</v>
       </c>
       <c r="B13" t="n">
-        <v>57654</v>
+        <v>79011</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1753,21 +1753,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>801305</v>
+        <v>801293</v>
       </c>
       <c r="R13" t="n">
-        <v>7403988</v>
+        <v>7403897</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1813,11 +1813,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1844,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127225133</v>
+        <v>127225070</v>
       </c>
       <c r="B14" t="n">
-        <v>78980</v>
+        <v>57654</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1855,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1879,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>801293</v>
+        <v>801305</v>
       </c>
       <c r="R14" t="n">
-        <v>7403897</v>
+        <v>7403988</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1915,6 +1910,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1944,7 +1944,7 @@
         <v>127225135</v>
       </c>
       <c r="B15" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2038,10 +2038,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127225141</v>
+        <v>127225072</v>
       </c>
       <c r="B16" t="n">
-        <v>78980</v>
+        <v>57654</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2049,21 +2049,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>801294</v>
+        <v>801496</v>
       </c>
       <c r="R16" t="n">
-        <v>7403990</v>
+        <v>7404005</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2109,6 +2109,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2135,10 +2140,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127225072</v>
+        <v>127225141</v>
       </c>
       <c r="B17" t="n">
-        <v>57654</v>
+        <v>79011</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2146,21 +2151,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2170,10 +2175,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>801496</v>
+        <v>801294</v>
       </c>
       <c r="R17" t="n">
-        <v>7404005</v>
+        <v>7403990</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2206,11 +2211,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 36487-2025 artfynd.xlsx
+++ b/artfynd/A 36487-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127225076</v>
       </c>
       <c r="B2" t="n">
-        <v>91615</v>
+        <v>91621</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127225066</v>
       </c>
       <c r="B3" t="n">
-        <v>91319</v>
+        <v>91325</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127225129</v>
       </c>
       <c r="B4" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127225078</v>
       </c>
       <c r="B5" t="n">
-        <v>97314</v>
+        <v>97320</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127225103</v>
+        <v>127225143</v>
       </c>
       <c r="B6" t="n">
-        <v>98436</v>
+        <v>79014</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>801366</v>
+        <v>801472</v>
       </c>
       <c r="R6" t="n">
-        <v>7404002</v>
+        <v>7404024</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127225143</v>
+        <v>127225103</v>
       </c>
       <c r="B7" t="n">
-        <v>79011</v>
+        <v>98442</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>801472</v>
+        <v>801366</v>
       </c>
       <c r="R7" t="n">
-        <v>7404024</v>
+        <v>7404002</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1257,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127225131</v>
+        <v>127225101</v>
       </c>
       <c r="B8" t="n">
-        <v>79011</v>
+        <v>98442</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>801287</v>
+        <v>801318</v>
       </c>
       <c r="R8" t="n">
-        <v>7403879</v>
+        <v>7403907</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1354,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127225101</v>
+        <v>127225131</v>
       </c>
       <c r="B9" t="n">
-        <v>98436</v>
+        <v>79014</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>801318</v>
+        <v>801287</v>
       </c>
       <c r="R9" t="n">
-        <v>7403907</v>
+        <v>7403879</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1454,7 +1454,7 @@
         <v>127225064</v>
       </c>
       <c r="B10" t="n">
-        <v>75135</v>
+        <v>75138</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>127225089</v>
       </c>
       <c r="B11" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>127225099</v>
       </c>
       <c r="B12" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>127225133</v>
       </c>
       <c r="B13" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>127225135</v>
       </c>
       <c r="B15" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>127225141</v>
       </c>
       <c r="B17" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 36487-2025 artfynd.xlsx
+++ b/artfynd/A 36487-2025 artfynd.xlsx
@@ -1257,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127225101</v>
+        <v>127225131</v>
       </c>
       <c r="B8" t="n">
-        <v>98442</v>
+        <v>79014</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>801318</v>
+        <v>801287</v>
       </c>
       <c r="R8" t="n">
-        <v>7403907</v>
+        <v>7403879</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1354,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127225131</v>
+        <v>127225101</v>
       </c>
       <c r="B9" t="n">
-        <v>79014</v>
+        <v>98442</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>801287</v>
+        <v>801318</v>
       </c>
       <c r="R9" t="n">
-        <v>7403879</v>
+        <v>7403907</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -2038,10 +2038,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127225072</v>
+        <v>127225141</v>
       </c>
       <c r="B16" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2049,21 +2049,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>801496</v>
+        <v>801294</v>
       </c>
       <c r="R16" t="n">
-        <v>7404005</v>
+        <v>7403990</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2109,11 +2109,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2140,10 +2135,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127225141</v>
+        <v>127225072</v>
       </c>
       <c r="B17" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2151,21 +2146,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2175,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>801294</v>
+        <v>801496</v>
       </c>
       <c r="R17" t="n">
-        <v>7403990</v>
+        <v>7404005</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2211,6 +2206,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 36487-2025 artfynd.xlsx
+++ b/artfynd/A 36487-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127225076</v>
       </c>
       <c r="B2" t="n">
-        <v>91621</v>
+        <v>91622</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127225066</v>
       </c>
       <c r="B3" t="n">
-        <v>91325</v>
+        <v>91326</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127225078</v>
       </c>
       <c r="B5" t="n">
-        <v>97320</v>
+        <v>97321</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>127225103</v>
       </c>
       <c r="B7" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>127225101</v>
       </c>
       <c r="B9" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>127225099</v>
       </c>
       <c r="B12" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2038,10 +2038,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127225141</v>
+        <v>127225072</v>
       </c>
       <c r="B16" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2049,21 +2049,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>801294</v>
+        <v>801496</v>
       </c>
       <c r="R16" t="n">
-        <v>7403990</v>
+        <v>7404005</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2109,6 +2109,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2135,10 +2140,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127225072</v>
+        <v>127225141</v>
       </c>
       <c r="B17" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2146,21 +2151,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2170,10 +2175,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>801496</v>
+        <v>801294</v>
       </c>
       <c r="R17" t="n">
-        <v>7404005</v>
+        <v>7403990</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2206,11 +2211,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 36487-2025 artfynd.xlsx
+++ b/artfynd/A 36487-2025 artfynd.xlsx
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127225143</v>
+        <v>127225103</v>
       </c>
       <c r="B6" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>801472</v>
+        <v>801366</v>
       </c>
       <c r="R6" t="n">
-        <v>7404024</v>
+        <v>7404002</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127225103</v>
+        <v>127225143</v>
       </c>
       <c r="B7" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>801366</v>
+        <v>801472</v>
       </c>
       <c r="R7" t="n">
-        <v>7404002</v>
+        <v>7404024</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127225133</v>
+        <v>127225070</v>
       </c>
       <c r="B13" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1753,21 +1753,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>801293</v>
+        <v>801305</v>
       </c>
       <c r="R13" t="n">
-        <v>7403897</v>
+        <v>7403988</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1813,6 +1813,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1839,10 +1844,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127225070</v>
+        <v>127225133</v>
       </c>
       <c r="B14" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,21 +1855,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>801305</v>
+        <v>801293</v>
       </c>
       <c r="R14" t="n">
-        <v>7403988</v>
+        <v>7403897</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1910,11 +1915,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 36487-2025 artfynd.xlsx
+++ b/artfynd/A 36487-2025 artfynd.xlsx
@@ -2038,10 +2038,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127225072</v>
+        <v>127225141</v>
       </c>
       <c r="B16" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2049,21 +2049,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>801496</v>
+        <v>801294</v>
       </c>
       <c r="R16" t="n">
-        <v>7404005</v>
+        <v>7403990</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2109,11 +2109,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2140,10 +2135,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127225141</v>
+        <v>127225072</v>
       </c>
       <c r="B17" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2151,21 +2146,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2175,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>801294</v>
+        <v>801496</v>
       </c>
       <c r="R17" t="n">
-        <v>7403990</v>
+        <v>7404005</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2211,6 +2206,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 36487-2025 artfynd.xlsx
+++ b/artfynd/A 36487-2025 artfynd.xlsx
@@ -1257,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127225131</v>
+        <v>127225101</v>
       </c>
       <c r="B8" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>801287</v>
+        <v>801318</v>
       </c>
       <c r="R8" t="n">
-        <v>7403879</v>
+        <v>7403907</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1354,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127225101</v>
+        <v>127225131</v>
       </c>
       <c r="B9" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>801318</v>
+        <v>801287</v>
       </c>
       <c r="R9" t="n">
-        <v>7403907</v>
+        <v>7403879</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -2038,10 +2038,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127225141</v>
+        <v>127225072</v>
       </c>
       <c r="B16" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2049,21 +2049,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>801294</v>
+        <v>801496</v>
       </c>
       <c r="R16" t="n">
-        <v>7403990</v>
+        <v>7404005</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2109,6 +2109,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2135,10 +2140,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127225072</v>
+        <v>127225141</v>
       </c>
       <c r="B17" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2146,21 +2151,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2170,10 +2175,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>801496</v>
+        <v>801294</v>
       </c>
       <c r="R17" t="n">
-        <v>7404005</v>
+        <v>7403990</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2206,11 +2211,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 36487-2025 artfynd.xlsx
+++ b/artfynd/A 36487-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127225076</v>
       </c>
       <c r="B2" t="n">
-        <v>91622</v>
+        <v>91626</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127225066</v>
       </c>
       <c r="B3" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127225129</v>
       </c>
       <c r="B4" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127225078</v>
       </c>
       <c r="B5" t="n">
-        <v>97321</v>
+        <v>97325</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>127225103</v>
       </c>
       <c r="B6" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>127225143</v>
       </c>
       <c r="B7" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1257,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127225101</v>
+        <v>127225131</v>
       </c>
       <c r="B8" t="n">
-        <v>98443</v>
+        <v>79018</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>801318</v>
+        <v>801287</v>
       </c>
       <c r="R8" t="n">
-        <v>7403907</v>
+        <v>7403879</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1354,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127225131</v>
+        <v>127225101</v>
       </c>
       <c r="B9" t="n">
-        <v>79014</v>
+        <v>98447</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>801287</v>
+        <v>801318</v>
       </c>
       <c r="R9" t="n">
-        <v>7403879</v>
+        <v>7403907</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1454,7 +1454,7 @@
         <v>127225064</v>
       </c>
       <c r="B10" t="n">
-        <v>75138</v>
+        <v>75142</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>127225089</v>
       </c>
       <c r="B11" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>127225099</v>
       </c>
       <c r="B12" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127225070</v>
+        <v>127225133</v>
       </c>
       <c r="B13" t="n">
-        <v>57654</v>
+        <v>79018</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1753,21 +1753,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>801305</v>
+        <v>801293</v>
       </c>
       <c r="R13" t="n">
-        <v>7403988</v>
+        <v>7403897</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1813,11 +1813,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1844,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127225133</v>
+        <v>127225070</v>
       </c>
       <c r="B14" t="n">
-        <v>79014</v>
+        <v>57658</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1855,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1879,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>801293</v>
+        <v>801305</v>
       </c>
       <c r="R14" t="n">
-        <v>7403897</v>
+        <v>7403988</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1915,6 +1910,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1944,7 +1944,7 @@
         <v>127225135</v>
       </c>
       <c r="B15" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>127225072</v>
       </c>
       <c r="B16" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>127225141</v>
       </c>
       <c r="B17" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 36487-2025 artfynd.xlsx
+++ b/artfynd/A 36487-2025 artfynd.xlsx
@@ -2038,10 +2038,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127225072</v>
+        <v>127225141</v>
       </c>
       <c r="B16" t="n">
-        <v>57658</v>
+        <v>79018</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2049,21 +2049,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>801496</v>
+        <v>801294</v>
       </c>
       <c r="R16" t="n">
-        <v>7404005</v>
+        <v>7403990</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2109,11 +2109,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2140,10 +2135,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127225141</v>
+        <v>127225072</v>
       </c>
       <c r="B17" t="n">
-        <v>79018</v>
+        <v>57658</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2151,21 +2146,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2175,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>801294</v>
+        <v>801496</v>
       </c>
       <c r="R17" t="n">
-        <v>7403990</v>
+        <v>7404005</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2211,6 +2206,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 36487-2025 artfynd.xlsx
+++ b/artfynd/A 36487-2025 artfynd.xlsx
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127225103</v>
+        <v>127225143</v>
       </c>
       <c r="B6" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>801366</v>
+        <v>801472</v>
       </c>
       <c r="R6" t="n">
-        <v>7404002</v>
+        <v>7404024</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127225143</v>
+        <v>127225103</v>
       </c>
       <c r="B7" t="n">
-        <v>79018</v>
+        <v>98447</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>801472</v>
+        <v>801366</v>
       </c>
       <c r="R7" t="n">
-        <v>7404024</v>
+        <v>7404002</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>

--- a/artfynd/A 36487-2025 artfynd.xlsx
+++ b/artfynd/A 36487-2025 artfynd.xlsx
@@ -1163,7 +1163,7 @@
         <v>127225103</v>
       </c>
       <c r="B7" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>127225101</v>
       </c>
       <c r="B9" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>127225099</v>
       </c>
       <c r="B12" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2038,10 +2038,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127225141</v>
+        <v>127225072</v>
       </c>
       <c r="B16" t="n">
-        <v>79018</v>
+        <v>57658</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2049,21 +2049,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>801294</v>
+        <v>801496</v>
       </c>
       <c r="R16" t="n">
-        <v>7403990</v>
+        <v>7404005</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2109,6 +2109,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2135,10 +2140,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127225072</v>
+        <v>127225141</v>
       </c>
       <c r="B17" t="n">
-        <v>57658</v>
+        <v>79018</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2146,21 +2151,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2170,10 +2175,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>801496</v>
+        <v>801294</v>
       </c>
       <c r="R17" t="n">
-        <v>7404005</v>
+        <v>7403990</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2206,11 +2211,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 36487-2025 artfynd.xlsx
+++ b/artfynd/A 36487-2025 artfynd.xlsx
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127225143</v>
+        <v>127225103</v>
       </c>
       <c r="B6" t="n">
-        <v>79018</v>
+        <v>98448</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>801472</v>
+        <v>801366</v>
       </c>
       <c r="R6" t="n">
-        <v>7404024</v>
+        <v>7404002</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127225103</v>
+        <v>127225143</v>
       </c>
       <c r="B7" t="n">
-        <v>98448</v>
+        <v>79018</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>801366</v>
+        <v>801472</v>
       </c>
       <c r="R7" t="n">
-        <v>7404002</v>
+        <v>7404024</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1257,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127225131</v>
+        <v>127225101</v>
       </c>
       <c r="B8" t="n">
-        <v>79018</v>
+        <v>98448</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>801287</v>
+        <v>801318</v>
       </c>
       <c r="R8" t="n">
-        <v>7403879</v>
+        <v>7403907</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1354,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127225101</v>
+        <v>127225131</v>
       </c>
       <c r="B9" t="n">
-        <v>98448</v>
+        <v>79018</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>801318</v>
+        <v>801287</v>
       </c>
       <c r="R9" t="n">
-        <v>7403907</v>
+        <v>7403879</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>

--- a/artfynd/A 36487-2025 artfynd.xlsx
+++ b/artfynd/A 36487-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>127225076</v>
       </c>
       <c r="B2" t="n">
-        <v>91626</v>
+        <v>91628</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127225066</v>
       </c>
       <c r="B3" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127225129</v>
       </c>
       <c r="B4" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127225078</v>
       </c>
       <c r="B5" t="n">
-        <v>97325</v>
+        <v>97327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127225103</v>
+        <v>127225143</v>
       </c>
       <c r="B6" t="n">
-        <v>98448</v>
+        <v>79020</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>801366</v>
+        <v>801472</v>
       </c>
       <c r="R6" t="n">
-        <v>7404002</v>
+        <v>7404024</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127225143</v>
+        <v>127225103</v>
       </c>
       <c r="B7" t="n">
-        <v>79018</v>
+        <v>98450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>801472</v>
+        <v>801366</v>
       </c>
       <c r="R7" t="n">
-        <v>7404024</v>
+        <v>7404002</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1257,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127225101</v>
+        <v>127225131</v>
       </c>
       <c r="B8" t="n">
-        <v>98448</v>
+        <v>79020</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>801318</v>
+        <v>801287</v>
       </c>
       <c r="R8" t="n">
-        <v>7403907</v>
+        <v>7403879</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1354,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127225131</v>
+        <v>127225101</v>
       </c>
       <c r="B9" t="n">
-        <v>79018</v>
+        <v>98450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>801287</v>
+        <v>801318</v>
       </c>
       <c r="R9" t="n">
-        <v>7403879</v>
+        <v>7403907</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1454,7 +1454,7 @@
         <v>127225064</v>
       </c>
       <c r="B10" t="n">
-        <v>75142</v>
+        <v>75144</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>127225089</v>
       </c>
       <c r="B11" t="n">
-        <v>78777</v>
+        <v>78779</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>127225099</v>
       </c>
       <c r="B12" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>127225133</v>
       </c>
       <c r="B13" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>127225070</v>
       </c>
       <c r="B14" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>127225135</v>
       </c>
       <c r="B15" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2038,10 +2038,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127225072</v>
+        <v>127225141</v>
       </c>
       <c r="B16" t="n">
-        <v>57658</v>
+        <v>79020</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2049,21 +2049,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>801496</v>
+        <v>801294</v>
       </c>
       <c r="R16" t="n">
-        <v>7404005</v>
+        <v>7403990</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2109,11 +2109,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2140,10 +2135,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127225141</v>
+        <v>127225072</v>
       </c>
       <c r="B17" t="n">
-        <v>79018</v>
+        <v>57660</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2151,21 +2146,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2175,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>801294</v>
+        <v>801496</v>
       </c>
       <c r="R17" t="n">
-        <v>7403990</v>
+        <v>7404005</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2213,6 +2208,11 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2234,6 +2234,642 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>127735583</v>
+      </c>
+      <c r="B18" t="n">
+        <v>98450</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Neitaskaite, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>801371</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7404007</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>127735581</v>
+      </c>
+      <c r="B19" t="n">
+        <v>91332</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Neitaskaite, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>801300</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7404002</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>127735579</v>
+      </c>
+      <c r="B20" t="n">
+        <v>91350</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Neitaskaite, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>801292</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7403857</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>127735582</v>
+      </c>
+      <c r="B21" t="n">
+        <v>91628</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>658</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Neitaskaite, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>801301</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7404002</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>127735595</v>
+      </c>
+      <c r="B22" t="n">
+        <v>98450</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Neitaskaite, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>801301</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7403875</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>127735580</v>
+      </c>
+      <c r="B23" t="n">
+        <v>98450</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Neitaskaite, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>801295</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7403864</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 36487-2025 artfynd.xlsx
+++ b/artfynd/A 36487-2025 artfynd.xlsx
@@ -2038,10 +2038,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127225141</v>
+        <v>127225072</v>
       </c>
       <c r="B16" t="n">
-        <v>79020</v>
+        <v>57660</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2049,21 +2049,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>801294</v>
+        <v>801496</v>
       </c>
       <c r="R16" t="n">
-        <v>7403990</v>
+        <v>7404005</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2109,6 +2109,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2135,10 +2140,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127225072</v>
+        <v>127225141</v>
       </c>
       <c r="B17" t="n">
-        <v>57660</v>
+        <v>79020</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2146,21 +2151,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2170,10 +2175,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>801496</v>
+        <v>801294</v>
       </c>
       <c r="R17" t="n">
-        <v>7404005</v>
+        <v>7403990</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2206,11 +2211,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2237,32 +2237,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127735583</v>
+        <v>127735581</v>
       </c>
       <c r="B18" t="n">
-        <v>98450</v>
+        <v>91332</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2276,10 +2276,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>801371</v>
+        <v>801300</v>
       </c>
       <c r="R18" t="n">
-        <v>7404007</v>
+        <v>7404002</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2343,32 +2343,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127735581</v>
+        <v>127735583</v>
       </c>
       <c r="B19" t="n">
-        <v>91332</v>
+        <v>98450</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2382,10 +2382,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>801300</v>
+        <v>801371</v>
       </c>
       <c r="R19" t="n">
-        <v>7404002</v>
+        <v>7404007</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2555,32 +2555,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127735582</v>
+        <v>127735595</v>
       </c>
       <c r="B21" t="n">
-        <v>91628</v>
+        <v>98450</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2597,7 +2597,7 @@
         <v>801301</v>
       </c>
       <c r="R21" t="n">
-        <v>7404002</v>
+        <v>7403875</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2661,32 +2661,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127735595</v>
+        <v>127735582</v>
       </c>
       <c r="B22" t="n">
-        <v>98450</v>
+        <v>91628</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2703,7 +2703,7 @@
         <v>801301</v>
       </c>
       <c r="R22" t="n">
-        <v>7403875</v>
+        <v>7404002</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 36487-2025 artfynd.xlsx
+++ b/artfynd/A 36487-2025 artfynd.xlsx
@@ -1257,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127225131</v>
+        <v>127225101</v>
       </c>
       <c r="B8" t="n">
-        <v>79020</v>
+        <v>98450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>801287</v>
+        <v>801318</v>
       </c>
       <c r="R8" t="n">
-        <v>7403879</v>
+        <v>7403907</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1354,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127225101</v>
+        <v>127225131</v>
       </c>
       <c r="B9" t="n">
-        <v>98450</v>
+        <v>79020</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>801318</v>
+        <v>801287</v>
       </c>
       <c r="R9" t="n">
-        <v>7403907</v>
+        <v>7403879</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>

--- a/artfynd/A 36487-2025 artfynd.xlsx
+++ b/artfynd/A 36487-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127225076</v>
       </c>
       <c r="B2" t="n">
-        <v>91628</v>
+        <v>91634</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127225066</v>
       </c>
       <c r="B3" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127225078</v>
       </c>
       <c r="B5" t="n">
-        <v>97327</v>
+        <v>97333</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>127225103</v>
       </c>
       <c r="B7" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1257,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127225101</v>
+        <v>127225131</v>
       </c>
       <c r="B8" t="n">
-        <v>98450</v>
+        <v>79020</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>801318</v>
+        <v>801287</v>
       </c>
       <c r="R8" t="n">
-        <v>7403907</v>
+        <v>7403879</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1354,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127225131</v>
+        <v>127225101</v>
       </c>
       <c r="B9" t="n">
-        <v>79020</v>
+        <v>98456</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>801287</v>
+        <v>801318</v>
       </c>
       <c r="R9" t="n">
-        <v>7403879</v>
+        <v>7403907</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1648,7 +1648,7 @@
         <v>127225099</v>
       </c>
       <c r="B12" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         <v>127735581</v>
       </c>
       <c r="B18" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2346,7 +2346,7 @@
         <v>127735583</v>
       </c>
       <c r="B19" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>127735579</v>
       </c>
       <c r="B20" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2555,32 +2555,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127735595</v>
+        <v>127735582</v>
       </c>
       <c r="B21" t="n">
-        <v>98450</v>
+        <v>91634</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2597,7 +2597,7 @@
         <v>801301</v>
       </c>
       <c r="R21" t="n">
-        <v>7403875</v>
+        <v>7404002</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2661,32 +2661,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127735582</v>
+        <v>127735595</v>
       </c>
       <c r="B22" t="n">
-        <v>91628</v>
+        <v>98456</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2703,7 +2703,7 @@
         <v>801301</v>
       </c>
       <c r="R22" t="n">
-        <v>7404002</v>
+        <v>7403875</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2770,7 +2770,7 @@
         <v>127735580</v>
       </c>
       <c r="B23" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 36487-2025 artfynd.xlsx
+++ b/artfynd/A 36487-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127225076</v>
       </c>
       <c r="B2" t="n">
-        <v>91634</v>
+        <v>91637</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127225066</v>
       </c>
       <c r="B3" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127225129</v>
       </c>
       <c r="B4" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127225078</v>
       </c>
       <c r="B5" t="n">
-        <v>97333</v>
+        <v>97336</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>127225143</v>
       </c>
       <c r="B6" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>127225103</v>
       </c>
       <c r="B7" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>127225131</v>
       </c>
       <c r="B8" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>127225101</v>
       </c>
       <c r="B9" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>127225064</v>
       </c>
       <c r="B10" t="n">
-        <v>75144</v>
+        <v>75147</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>127225089</v>
       </c>
       <c r="B11" t="n">
-        <v>78779</v>
+        <v>78782</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>127225099</v>
       </c>
       <c r="B12" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>127225133</v>
       </c>
       <c r="B13" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>127225070</v>
       </c>
       <c r="B14" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>127225135</v>
       </c>
       <c r="B15" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>127225072</v>
       </c>
       <c r="B16" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>127225141</v>
       </c>
       <c r="B17" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         <v>127735581</v>
       </c>
       <c r="B18" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2346,7 +2346,7 @@
         <v>127735583</v>
       </c>
       <c r="B19" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>127735579</v>
       </c>
       <c r="B20" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>127735582</v>
       </c>
       <c r="B21" t="n">
-        <v>91634</v>
+        <v>91637</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>127735595</v>
       </c>
       <c r="B22" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
         <v>127735580</v>
       </c>
       <c r="B23" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 36487-2025 artfynd.xlsx
+++ b/artfynd/A 36487-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127225076</v>
       </c>
       <c r="B2" t="n">
-        <v>91637</v>
+        <v>91645</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127225066</v>
       </c>
       <c r="B3" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127225129</v>
       </c>
       <c r="B4" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127225078</v>
       </c>
       <c r="B5" t="n">
-        <v>97336</v>
+        <v>97344</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127225143</v>
+        <v>127225103</v>
       </c>
       <c r="B6" t="n">
-        <v>79023</v>
+        <v>98467</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>801472</v>
+        <v>801366</v>
       </c>
       <c r="R6" t="n">
-        <v>7404024</v>
+        <v>7404002</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127225103</v>
+        <v>127225143</v>
       </c>
       <c r="B7" t="n">
-        <v>98459</v>
+        <v>79029</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>801366</v>
+        <v>801472</v>
       </c>
       <c r="R7" t="n">
-        <v>7404002</v>
+        <v>7404024</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1260,7 +1260,7 @@
         <v>127225131</v>
       </c>
       <c r="B8" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>127225101</v>
       </c>
       <c r="B9" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>127225064</v>
       </c>
       <c r="B10" t="n">
-        <v>75147</v>
+        <v>75153</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>127225089</v>
       </c>
       <c r="B11" t="n">
-        <v>78782</v>
+        <v>78788</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>127225099</v>
       </c>
       <c r="B12" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>127225133</v>
       </c>
       <c r="B13" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>127225070</v>
       </c>
       <c r="B14" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>127225135</v>
       </c>
       <c r="B15" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>127225072</v>
       </c>
       <c r="B16" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>127225141</v>
       </c>
       <c r="B17" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         <v>127735581</v>
       </c>
       <c r="B18" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2346,7 +2346,7 @@
         <v>127735583</v>
       </c>
       <c r="B19" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>127735579</v>
       </c>
       <c r="B20" t="n">
-        <v>91359</v>
+        <v>91367</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>127735582</v>
       </c>
       <c r="B21" t="n">
-        <v>91637</v>
+        <v>91645</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>127735595</v>
       </c>
       <c r="B22" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
         <v>127735580</v>
       </c>
       <c r="B23" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 36487-2025 artfynd.xlsx
+++ b/artfynd/A 36487-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127225076</v>
       </c>
       <c r="B2" t="n">
-        <v>91645</v>
+        <v>91646</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127225066</v>
       </c>
       <c r="B3" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127225078</v>
       </c>
       <c r="B5" t="n">
-        <v>97344</v>
+        <v>97345</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127225103</v>
+        <v>127225143</v>
       </c>
       <c r="B6" t="n">
-        <v>98467</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>801366</v>
+        <v>801472</v>
       </c>
       <c r="R6" t="n">
-        <v>7404002</v>
+        <v>7404024</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127225143</v>
+        <v>127225103</v>
       </c>
       <c r="B7" t="n">
-        <v>79029</v>
+        <v>98468</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>801472</v>
+        <v>801366</v>
       </c>
       <c r="R7" t="n">
-        <v>7404024</v>
+        <v>7404002</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1257,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127225131</v>
+        <v>127225101</v>
       </c>
       <c r="B8" t="n">
-        <v>79029</v>
+        <v>98468</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>801287</v>
+        <v>801318</v>
       </c>
       <c r="R8" t="n">
-        <v>7403879</v>
+        <v>7403907</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1354,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127225101</v>
+        <v>127225131</v>
       </c>
       <c r="B9" t="n">
-        <v>98467</v>
+        <v>79029</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>801318</v>
+        <v>801287</v>
       </c>
       <c r="R9" t="n">
-        <v>7403907</v>
+        <v>7403879</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1648,7 +1648,7 @@
         <v>127225099</v>
       </c>
       <c r="B12" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2237,32 +2237,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127735581</v>
+        <v>127735583</v>
       </c>
       <c r="B18" t="n">
-        <v>91349</v>
+        <v>98468</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2276,10 +2276,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>801300</v>
+        <v>801371</v>
       </c>
       <c r="R18" t="n">
-        <v>7404002</v>
+        <v>7404007</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2343,32 +2343,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127735583</v>
+        <v>127735581</v>
       </c>
       <c r="B19" t="n">
-        <v>98467</v>
+        <v>91350</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2382,10 +2382,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>801371</v>
+        <v>801300</v>
       </c>
       <c r="R19" t="n">
-        <v>7404007</v>
+        <v>7404002</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2452,7 +2452,7 @@
         <v>127735579</v>
       </c>
       <c r="B20" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>127735582</v>
       </c>
       <c r="B21" t="n">
-        <v>91645</v>
+        <v>91646</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>127735595</v>
       </c>
       <c r="B22" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
         <v>127735580</v>
       </c>
       <c r="B23" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 36487-2025 artfynd.xlsx
+++ b/artfynd/A 36487-2025 artfynd.xlsx
@@ -2237,32 +2237,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127735583</v>
+        <v>127735581</v>
       </c>
       <c r="B18" t="n">
-        <v>98468</v>
+        <v>91350</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2276,10 +2276,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>801371</v>
+        <v>801300</v>
       </c>
       <c r="R18" t="n">
-        <v>7404007</v>
+        <v>7404002</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2343,32 +2343,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127735581</v>
+        <v>127735583</v>
       </c>
       <c r="B19" t="n">
-        <v>91350</v>
+        <v>98468</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2382,10 +2382,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>801300</v>
+        <v>801371</v>
       </c>
       <c r="R19" t="n">
-        <v>7404002</v>
+        <v>7404007</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2555,32 +2555,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127735582</v>
+        <v>127735595</v>
       </c>
       <c r="B21" t="n">
-        <v>91646</v>
+        <v>98468</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2597,7 +2597,7 @@
         <v>801301</v>
       </c>
       <c r="R21" t="n">
-        <v>7404002</v>
+        <v>7403875</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2661,32 +2661,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127735595</v>
+        <v>127735582</v>
       </c>
       <c r="B22" t="n">
-        <v>98468</v>
+        <v>91646</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2703,7 +2703,7 @@
         <v>801301</v>
       </c>
       <c r="R22" t="n">
-        <v>7403875</v>
+        <v>7404002</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 36487-2025 artfynd.xlsx
+++ b/artfynd/A 36487-2025 artfynd.xlsx
@@ -2240,7 +2240,7 @@
         <v>127735581</v>
       </c>
       <c r="B18" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2346,7 +2346,7 @@
         <v>127735583</v>
       </c>
       <c r="B19" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>127735579</v>
       </c>
       <c r="B20" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>127735595</v>
       </c>
       <c r="B21" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>127735582</v>
       </c>
       <c r="B22" t="n">
-        <v>91646</v>
+        <v>91647</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
         <v>127735580</v>
       </c>
       <c r="B23" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 36487-2025 artfynd.xlsx
+++ b/artfynd/A 36487-2025 artfynd.xlsx
@@ -2237,32 +2237,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127735581</v>
+        <v>127735583</v>
       </c>
       <c r="B18" t="n">
-        <v>91351</v>
+        <v>98470</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2276,10 +2276,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>801300</v>
+        <v>801371</v>
       </c>
       <c r="R18" t="n">
-        <v>7404002</v>
+        <v>7404007</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2343,32 +2343,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127735583</v>
+        <v>127735581</v>
       </c>
       <c r="B19" t="n">
-        <v>98469</v>
+        <v>91352</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2382,10 +2382,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>801371</v>
+        <v>801300</v>
       </c>
       <c r="R19" t="n">
-        <v>7404007</v>
+        <v>7404002</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2452,7 +2452,7 @@
         <v>127735579</v>
       </c>
       <c r="B20" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>127735595</v>
       </c>
       <c r="B21" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>127735582</v>
       </c>
       <c r="B22" t="n">
-        <v>91647</v>
+        <v>91648</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
         <v>127735580</v>
       </c>
       <c r="B23" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 36487-2025 artfynd.xlsx
+++ b/artfynd/A 36487-2025 artfynd.xlsx
@@ -2237,32 +2237,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127735583</v>
+        <v>127735581</v>
       </c>
       <c r="B18" t="n">
-        <v>98470</v>
+        <v>91352</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2276,10 +2276,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>801371</v>
+        <v>801300</v>
       </c>
       <c r="R18" t="n">
-        <v>7404007</v>
+        <v>7404002</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2343,32 +2343,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127735581</v>
+        <v>127735583</v>
       </c>
       <c r="B19" t="n">
-        <v>91352</v>
+        <v>98470</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2382,10 +2382,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>801300</v>
+        <v>801371</v>
       </c>
       <c r="R19" t="n">
-        <v>7404002</v>
+        <v>7404007</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 36487-2025 artfynd.xlsx
+++ b/artfynd/A 36487-2025 artfynd.xlsx
@@ -2237,32 +2237,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127735581</v>
+        <v>127735583</v>
       </c>
       <c r="B18" t="n">
-        <v>91352</v>
+        <v>98470</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2276,10 +2276,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>801300</v>
+        <v>801371</v>
       </c>
       <c r="R18" t="n">
-        <v>7404002</v>
+        <v>7404007</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2343,32 +2343,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127735583</v>
+        <v>127735581</v>
       </c>
       <c r="B19" t="n">
-        <v>98470</v>
+        <v>91352</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2382,10 +2382,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>801371</v>
+        <v>801300</v>
       </c>
       <c r="R19" t="n">
-        <v>7404007</v>
+        <v>7404002</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 36487-2025 artfynd.xlsx
+++ b/artfynd/A 36487-2025 artfynd.xlsx
@@ -2240,7 +2240,7 @@
         <v>127735583</v>
       </c>
       <c r="B18" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2346,7 +2346,7 @@
         <v>127735581</v>
       </c>
       <c r="B19" t="n">
-        <v>91352</v>
+        <v>91360</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>127735579</v>
       </c>
       <c r="B20" t="n">
-        <v>91370</v>
+        <v>91378</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>127735595</v>
       </c>
       <c r="B21" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>127735582</v>
       </c>
       <c r="B22" t="n">
-        <v>91648</v>
+        <v>91656</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
         <v>127735580</v>
       </c>
       <c r="B23" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 36487-2025 artfynd.xlsx
+++ b/artfynd/A 36487-2025 artfynd.xlsx
@@ -2237,32 +2237,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127735583</v>
+        <v>127735581</v>
       </c>
       <c r="B18" t="n">
-        <v>98478</v>
+        <v>91452</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2276,10 +2276,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>801371</v>
+        <v>801300</v>
       </c>
       <c r="R18" t="n">
-        <v>7404007</v>
+        <v>7404002</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2343,32 +2343,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127735581</v>
+        <v>127735583</v>
       </c>
       <c r="B19" t="n">
-        <v>91360</v>
+        <v>98571</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2382,10 +2382,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>801300</v>
+        <v>801371</v>
       </c>
       <c r="R19" t="n">
-        <v>7404002</v>
+        <v>7404007</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2452,7 +2452,7 @@
         <v>127735579</v>
       </c>
       <c r="B20" t="n">
-        <v>91378</v>
+        <v>91470</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>127735595</v>
       </c>
       <c r="B21" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>127735582</v>
       </c>
       <c r="B22" t="n">
-        <v>91656</v>
+        <v>91748</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
         <v>127735580</v>
       </c>
       <c r="B23" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
